--- a/VerveStacks_NOR_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NOR_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DABA4A6-5D2A-4719-B9DC-B93F36983D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D6B2EB-DE73-4D37-84B2-59627CFF8D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5009,7 +5009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054BF30A-6AB4-4DA9-A932-E9379CDBC5E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB6F38E-A7E1-4D4E-B8F4-54DDB977E67E}">
   <dimension ref="B2:AG1192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30942,7 +30942,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2837C3-A7F7-4B3C-82CF-71CB5FA6D84D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2288A4CE-6439-4604-A149-83079A43793B}">
   <dimension ref="B9:L29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43455,7 +43455,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{954C26E1-8686-437A-99EF-08122CA225FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD403C8-8EA7-4ECF-A457-450DE47EF751}">
   <dimension ref="A1:I75"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
